--- a/tasks/finalpool/terminal-sf-wc-yf-excel-ppt/groundtruth_workspace/Executive_Dashboard.xlsx
+++ b/tasks/finalpool/terminal-sf-wc-yf-excel-ppt/groundtruth_workspace/Executive_Dashboard.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20713.32</v>
+        <v>19773.58</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>411.41</v>
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17524.84</v>
+        <v>16692.24</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>411.41</v>
@@ -593,14 +593,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Speakers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12398</v>
+        <v>6205.12</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>411.41</v>
@@ -609,14 +609,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Watches</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2501.57</v>
+        <v>6160.7</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>411.41</v>
@@ -625,14 +625,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cameras</t>
+          <t>Watches</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2369.28</v>
+        <v>2486.57</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>411.41</v>
@@ -641,16 +641,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Cameras</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2351.22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>411.41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Home Appliances</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1928.2</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B8" t="n">
+        <v>1916.16</v>
+      </c>
+      <c r="C8" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>411.41</v>
       </c>
     </row>
@@ -711,7 +727,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon.com Inc</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
     </row>
@@ -726,7 +742,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
     </row>
